--- a/mixs-templates/Mimag_plus_combinations/MimagWater.xlsx
+++ b/mixs-templates/Mimag_plus_combinations/MimagWater.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EK1"/>
+  <dimension ref="A1:EM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,500 +624,510 @@
       </c>
       <c r="AP1" t="inlineStr">
         <is>
+          <t>marker_gene_recov</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>marker_gene_recov_sw</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>feat_pred</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>compl_software</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>sim_search_meth</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>compl_appr</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>samp_taxon_id</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>collection_date</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>seq_meth</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>lat_lon</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>tax_class</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>experimental_factor</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>sop</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>alkalinity</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>alkalinity_method</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>alkyl_diethers</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>aminopept_act</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>ammonium</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>atmospheric_data</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>bacteria_carb_prod</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>bac_prod</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>bac_resp</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>biomass</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>bishomohopanol</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>bromide</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>calcium</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>carb_nitro_ratio</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>chem_administration</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>chloride</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>chlorophyll</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>conduc</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>density</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>diether_lipids</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>diss_carb_dioxide</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>diss_hydrogen</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>diss_inorg_carb</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>diss_inorg_nitro</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>diss_inorg_phosp</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>diss_org_carb</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>diss_org_nitro</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>diss_oxygen</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>down_par</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>fluor</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>glucosidase_act</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>light_intensity</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>magnesium</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>mean_frict_vel</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>mean_peak_frict_vel</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>misc_param</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>n_alkanes</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>nitrate</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>nitrite</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>nitro</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>org_carb</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>org_matter</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>org_nitro</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>organism_count</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>oxy_stat_samp</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>ph</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>part_org_carb</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>part_org_nitro</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>perturbation</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>petroleum_hydrocarb</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>phaeopigments</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>phosphate</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>phosplipid_fatt_acid</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>photon_flux</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>potassium</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>pressure</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>primary_prod</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>redox_potential</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>salinity</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>samp_store_dur</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>samp_store_loc</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>samp_store_temp</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>silicate</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>size_frac_low</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>size_frac_up</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>sodium</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>soluble_react_phosp</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>sulfate</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>sulfide</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>suspend_part_matter</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>tidal_stage</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>tot_depth_water_col</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>tot_diss_nitro</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>tot_inorg_nitro</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>tot_nitro</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>tot_part_carb</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>tot_phosp</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>turbidity</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>water_current</t>
         </is>
@@ -1149,13 +1159,13 @@
     <dataValidation sqref="AK2:AK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"16S rRNA gene,multi-marker approach,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ2:AZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"marker gene,other,reference based"</formula1>
     </dataValidation>
-    <dataValidation sqref="DC2:DC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="DE2:DE1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"aerobic,anaerobic,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="EC2:EC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="EE2:EE1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ebb tide,flood tide,high tide,low tide"</formula1>
     </dataValidation>
   </dataValidations>
